--- a/SQExcel.Portal/src/content/docs/ja/docs/images/small-scale/small-scale.xlsx
+++ b/SQExcel.Portal/src/content/docs/ja/docs/images/small-scale/small-scale.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos_MS\East\SQL2Excel\v100\SQL2Excel\SQL2Excel.Help\src\content\docs\ja\images\small-scale\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos_GitEms\sqexcel\SQExcel.Portal\src\content\docs\ja\docs\images\small-scale\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{696E184C-9531-4EE0-A7CD-C2ADDD692E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BF6A23A-E249-4C66-9F16-FB8F57B387E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1280" yWindow="1670" windowWidth="20820" windowHeight="13610" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="22224" windowHeight="14736" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SMALL_SCALE" sheetId="5" r:id="rId1"/>
@@ -2155,243 +2155,6 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>224118</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>7472</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>217768</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>117250</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="図 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D01C241B-A0C4-EC03-1E7D-DA12F06EFC51}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="455706" y="10892119"/>
-          <a:ext cx="10646709" cy="6594249"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>49</xdr:col>
-      <xdr:colOff>74706</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>72339</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="12" name="グループ化 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75212CCE-9B29-3B1F-059C-79C6061EF998}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="463176" y="1389529"/>
-          <a:ext cx="10959354" cy="7946339"/>
-          <a:chOff x="469900" y="1371600"/>
-          <a:chExt cx="11117356" cy="7844739"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="8" name="図 7">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3DC96A44-A72B-B408-3031-7D33BEEBAEBA}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="469900" y="1371600"/>
-            <a:ext cx="10801952" cy="7844739"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="6" name="正方形/長方形 5">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4CBF565-CED4-4BE7-B362-930D583358D6}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3976593" y="6166291"/>
-            <a:ext cx="6988322" cy="2403607"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="7" name="吹き出し: 四角形 6">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D790E08-B69F-4BE9-8BA7-FF27D0E75E81}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="9657273" y="7927962"/>
-            <a:ext cx="1929983" cy="538169"/>
-          </a:xfrm>
-          <a:prstGeom prst="wedgeRectCallout">
-            <a:avLst>
-              <a:gd name="adj1" fmla="val -68243"/>
-              <a:gd name="adj2" fmla="val -37145"/>
-            </a:avLst>
-          </a:prstGeom>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent2"/>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="lt1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent2"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="dk1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>接続設定項目は</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1000">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>PostgreSQL</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>用のものです。</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>37</xdr:col>
       <xdr:colOff>61417</xdr:colOff>
       <xdr:row>51</xdr:row>
@@ -2458,279 +2221,6 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>182880</xdr:colOff>
-      <xdr:row>117</xdr:row>
-      <xdr:rowOff>89647</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="23" name="グループ化 22">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B9AB832-B14F-6A0C-A7CA-118588E641CA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="463176" y="18990235"/>
-          <a:ext cx="8520057" cy="8195236"/>
-          <a:chOff x="469900" y="18745200"/>
-          <a:chExt cx="8641080" cy="8090647"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="18" name="図 17">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{278DCDED-85FA-A0F9-CE09-8E20A56C046F}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="469900" y="18745200"/>
-            <a:ext cx="8641080" cy="8070879"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="19" name="正方形/長方形 18">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5B4398F-7A82-40F4-877B-1D7229AADFFB}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="611840" y="19955435"/>
-            <a:ext cx="6071346" cy="325718"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="21" name="正方形/長方形 20">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4EED837A-BDD5-49DF-B7B3-BC4DA723472D}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="634254" y="21165670"/>
-            <a:ext cx="6146051" cy="322731"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="22" name="正方形/長方形 21">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9048245-B224-422B-829E-62CD4116B857}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="6183406" y="26386118"/>
-            <a:ext cx="1301750" cy="449729"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>123</xdr:row>
-      <xdr:rowOff>99785</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>148</xdr:row>
-      <xdr:rowOff>122186</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="25" name="図 24">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0C7E3C8-85FE-9312-CE20-94E8039B1803}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="471714" y="27994428"/>
-          <a:ext cx="10842172" cy="5692044"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
@@ -2805,378 +2295,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>224118</xdr:colOff>
-      <xdr:row>156</xdr:row>
-      <xdr:rowOff>59765</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>221130</xdr:colOff>
-      <xdr:row>178</xdr:row>
-      <xdr:rowOff>101760</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="30" name="図 29">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E79CB67-1C27-DF65-EEF7-CB1FD0F95F4C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="455706" y="35724353"/>
-          <a:ext cx="10650071" cy="5136936"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>29882</xdr:colOff>
-      <xdr:row>186</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>48</xdr:col>
-      <xdr:colOff>26894</xdr:colOff>
-      <xdr:row>208</xdr:row>
-      <xdr:rowOff>41994</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="31" name="図 30">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E9DA14B-FEAB-28F8-DD42-7D52B449887C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="493058" y="43075412"/>
-          <a:ext cx="10650071" cy="5136935"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>209177</xdr:colOff>
-      <xdr:row>249</xdr:row>
-      <xdr:rowOff>29884</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>160469</xdr:colOff>
-      <xdr:row>284</xdr:row>
-      <xdr:rowOff>218141</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="41" name="グループ化 40">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7265AD7-533E-0764-33DB-64BD129867E2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="440765" y="57695355"/>
-          <a:ext cx="8520057" cy="8293845"/>
-          <a:chOff x="444127" y="50550484"/>
-          <a:chExt cx="8644442" cy="8189257"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="33" name="図 32">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49B956C1-EE7B-0211-5024-43A26CE90387}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="444127" y="50550484"/>
-            <a:ext cx="8644442" cy="8189257"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="37" name="正方形/長方形 36">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBD5C3DB-E2A5-4D00-83ED-384A123F8EC5}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="604371" y="54526331"/>
-            <a:ext cx="835213" cy="213658"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="38" name="正方形/長方形 37">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0B0BF1F-E5D2-1568-599D-72B7A06B0DF8}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="622298" y="53562625"/>
-            <a:ext cx="6363075" cy="439268"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="39" name="正方形/長方形 38">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90237E61-4834-C912-A376-430CA662281B}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="4818528" y="54166248"/>
-            <a:ext cx="2017433" cy="213658"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="40" name="正方形/長方形 39">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4CE0AEEE-7557-4527-83FC-6206014EE55D}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="6310406" y="58405058"/>
-            <a:ext cx="1260288" cy="288366"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>44824</xdr:colOff>
       <xdr:row>290</xdr:row>
@@ -3202,7 +2320,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3246,7 +2364,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3290,7 +2408,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3310,22 +2428,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>22412</xdr:colOff>
-      <xdr:row>214</xdr:row>
-      <xdr:rowOff>29882</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>48</xdr:col>
-      <xdr:colOff>19424</xdr:colOff>
-      <xdr:row>236</xdr:row>
-      <xdr:rowOff>181279</xdr:rowOff>
+      <xdr:col>49</xdr:col>
+      <xdr:colOff>74706</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>72339</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="9" name="グループ化 8">
+        <xdr:cNvPr id="13" name="グループ化 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2B1C954-3CDE-0111-D292-86D05AFAB106}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA1B0DCB-4E9C-35C2-CA77-E4F815A6AC22}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3333,18 +2451,993 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="485588" y="49589764"/>
-          <a:ext cx="10650071" cy="5246339"/>
-          <a:chOff x="477371" y="48706741"/>
-          <a:chExt cx="10804712" cy="5180598"/>
+          <a:off x="466165" y="1398494"/>
+          <a:ext cx="11029576" cy="7997139"/>
+          <a:chOff x="472440" y="1371600"/>
+          <a:chExt cx="11177046" cy="7844739"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="12" name="グループ化 11">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75212CCE-9B29-3B1F-059C-79C6061EF998}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="472440" y="1371600"/>
+            <a:ext cx="11177046" cy="7844739"/>
+            <a:chOff x="469900" y="1371600"/>
+            <a:chExt cx="11117356" cy="7844739"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="8" name="図 7">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3DC96A44-A72B-B408-3031-7D33BEEBAEBA}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="469900" y="1371600"/>
+              <a:ext cx="10801952" cy="7844739"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="6" name="正方形/長方形 5">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4CBF565-CED4-4BE7-B362-930D583358D6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3976593" y="6166291"/>
+              <a:ext cx="6988322" cy="2403607"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="7" name="吹き出し: 四角形 6">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D790E08-B69F-4BE9-8BA7-FF27D0E75E81}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="9657273" y="7927962"/>
+              <a:ext cx="1929983" cy="538169"/>
+            </a:xfrm>
+            <a:prstGeom prst="wedgeRectCallout">
+              <a:avLst>
+                <a:gd name="adj1" fmla="val -68243"/>
+                <a:gd name="adj2" fmla="val -37145"/>
+              </a:avLst>
+            </a:prstGeom>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent2"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent2"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>接続設定項目は</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1000">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>PostgreSQL</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>用のものです。</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="11" name="図 10">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE5C1EA0-71F6-4219-8887-7F7C9F31BD63}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="517264" y="1425388"/>
+            <a:ext cx="250353" cy="221456"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>224118</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>7472</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>217768</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>117250</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="16" name="グループ化 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A02798E2-220F-B8C9-5270-DE8FB03C855D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="457200" y="10962343"/>
+          <a:ext cx="10715439" cy="6636083"/>
+          <a:chOff x="460338" y="10751672"/>
+          <a:chExt cx="10859770" cy="6510578"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="2" name="図 1">
+          <xdr:cNvPr id="10" name="図 9">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6628907-6B5B-FD07-FEC7-57805877FF59}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D01C241B-A0C4-EC03-1E7D-DA12F06EFC51}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="460338" y="10751672"/>
+            <a:ext cx="10859770" cy="6510578"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="15" name="図 14">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2118B0B7-A4E3-4615-989C-241C3EF6A6D5}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="526228" y="10780058"/>
+            <a:ext cx="212717" cy="214624"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>182880</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>89647</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="20" name="グループ化 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{004BEE26-B85E-732A-011A-438BA5665869}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="466165" y="19112753"/>
+          <a:ext cx="8573844" cy="8247529"/>
+          <a:chOff x="472440" y="18745200"/>
+          <a:chExt cx="8686800" cy="8090647"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="23" name="グループ化 22">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B9AB832-B14F-6A0C-A7CA-118588E641CA}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="472440" y="18745200"/>
+            <a:ext cx="8686800" cy="8090647"/>
+            <a:chOff x="469900" y="18745200"/>
+            <a:chExt cx="8641080" cy="8090647"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="18" name="図 17">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{278DCDED-85FA-A0F9-CE09-8E20A56C046F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="469900" y="18745200"/>
+              <a:ext cx="8641080" cy="8070879"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="19" name="正方形/長方形 18">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5B4398F-7A82-40F4-877B-1D7229AADFFB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="611840" y="19955435"/>
+              <a:ext cx="6071346" cy="325718"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="21" name="正方形/長方形 20">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4EED837A-BDD5-49DF-B7B3-BC4DA723472D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="634254" y="21165670"/>
+              <a:ext cx="6146051" cy="322731"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="22" name="正方形/長方形 21">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9048245-B224-422B-829E-62CD4116B857}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6183406" y="26386118"/>
+              <a:ext cx="1301750" cy="449729"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="17" name="図 16">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{018D3EF2-E8CA-40D2-98C4-9AEFBB99C0D3}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="580017" y="18816917"/>
+            <a:ext cx="212717" cy="214624"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>209177</xdr:colOff>
+      <xdr:row>249</xdr:row>
+      <xdr:rowOff>29884</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>160469</xdr:colOff>
+      <xdr:row>284</xdr:row>
+      <xdr:rowOff>218141</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="45" name="グループ化 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA4EE942-B9AF-6028-E28F-4849BF962B6B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="442259" y="58067390"/>
+          <a:ext cx="8575339" cy="8346139"/>
+          <a:chOff x="445397" y="56951284"/>
+          <a:chExt cx="8691432" cy="8189257"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="41" name="グループ化 40">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7265AD7-533E-0764-33DB-64BD129867E2}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="445397" y="56951284"/>
+            <a:ext cx="8691432" cy="8189257"/>
+            <a:chOff x="444127" y="50550484"/>
+            <a:chExt cx="8644442" cy="8189257"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="33" name="図 32">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49B956C1-EE7B-0211-5024-43A26CE90387}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="444127" y="50550484"/>
+              <a:ext cx="8644442" cy="8189257"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="37" name="正方形/長方形 36">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBD5C3DB-E2A5-4D00-83ED-384A123F8EC5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="604371" y="54526331"/>
+              <a:ext cx="835213" cy="213658"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="38" name="正方形/長方形 37">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0B0BF1F-E5D2-1568-599D-72B7A06B0DF8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="622298" y="53562625"/>
+              <a:ext cx="6363075" cy="439268"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="39" name="正方形/長方形 38">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90237E61-4834-C912-A376-430CA662281B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4818528" y="54166248"/>
+              <a:ext cx="2017433" cy="213658"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="40" name="正方形/長方形 39">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4CE0AEEE-7557-4527-83FC-6206014EE55D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6310406" y="58405058"/>
+              <a:ext cx="1260288" cy="288366"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="36" name="図 35">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{50259E43-5744-47FD-86D8-C1F9F3C70D59}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="526228" y="57011047"/>
+            <a:ext cx="212717" cy="214624"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>123</xdr:row>
+      <xdr:rowOff>99785</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>148</xdr:row>
+      <xdr:rowOff>122186</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="47" name="グループ化 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FA42669-CA92-9E3A-3901-69B8AC7AF386}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="466165" y="28768914"/>
+          <a:ext cx="10717306" cy="5849460"/>
+          <a:chOff x="472440" y="28217585"/>
+          <a:chExt cx="10858500" cy="5737401"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="25" name="図 24">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0C7E3C8-85FE-9312-CE20-94E8039B1803}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="472440" y="28217585"/>
+            <a:ext cx="10858500" cy="5737401"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="46" name="図 45">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E24885A9-EEB2-EE4A-5DBF-8751C728CED1}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3360,190 +3453,489 @@
         </xdr:blipFill>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="477371" y="48706741"/>
-            <a:ext cx="10804712" cy="5180598"/>
+            <a:off x="8260079" y="29519880"/>
+            <a:ext cx="2889513" cy="182880"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
           </a:prstGeom>
         </xdr:spPr>
       </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="3" name="正方形/長方形 2">
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>224118</xdr:colOff>
+      <xdr:row>156</xdr:row>
+      <xdr:rowOff>59765</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>221130</xdr:colOff>
+      <xdr:row>178</xdr:row>
+      <xdr:rowOff>101760</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="50" name="グループ化 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3016DDE-4DED-22C1-EEB3-0890B3111AA2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="457200" y="36420612"/>
+          <a:ext cx="10718801" cy="5169807"/>
+          <a:chOff x="460338" y="35721365"/>
+          <a:chExt cx="10863132" cy="5071195"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="30" name="図 29">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30A5B41C-2C27-49CB-AA8A-912A8FE740E3}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E79CB67-1C27-DF65-EEF7-CB1FD0F95F4C}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="1801532" y="49961801"/>
-            <a:ext cx="2532156" cy="198717"/>
+            <a:off x="460338" y="35721365"/>
+            <a:ext cx="10863132" cy="5071195"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
           </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
         </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="4" name="吹き出し: 四角形 3">
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="49" name="図 48">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3F86FF4-84B0-412F-BF48-1FE088B6FEE6}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC85DB52-06B6-255D-B144-3A8FB4B7058F}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="878727" y="52565485"/>
-            <a:ext cx="2170580" cy="666190"/>
-          </a:xfrm>
-          <a:prstGeom prst="wedgeRectCallout">
-            <a:avLst>
-              <a:gd name="adj1" fmla="val -8906"/>
-              <a:gd name="adj2" fmla="val 81250"/>
-            </a:avLst>
-          </a:prstGeom>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent2"/>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="lt1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent2"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="dk1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1000">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>common_codes</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>シート側でも処理結果は成功となっています。</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="5" name="正方形/長方形 4">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E287D2A6-70F9-F934-BD63-AAF340A68FB0}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="1361515" y="53443094"/>
-            <a:ext cx="1827306" cy="258484"/>
+            <a:off x="6042660" y="36804601"/>
+            <a:ext cx="4076700" cy="191672"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
           </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
         </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>29882</xdr:colOff>
+      <xdr:row>186</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>26894</xdr:colOff>
+      <xdr:row>208</xdr:row>
+      <xdr:rowOff>41994</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="53" name="グループ化 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{258D6483-4E57-6069-D9DC-A0C68441263E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="496047" y="43353318"/>
+          <a:ext cx="10718800" cy="5169805"/>
+          <a:chOff x="502322" y="42519600"/>
+          <a:chExt cx="10863132" cy="5071194"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="31" name="図 30">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E9DA14B-FEAB-28F8-DD42-7D52B449887C}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="502322" y="42519600"/>
+            <a:ext cx="10863132" cy="5071194"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="52" name="図 51">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE22555D-A95C-1FFF-28F6-F3CD21CF0BC2}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="6233160" y="43601640"/>
+            <a:ext cx="2125980" cy="178354"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>22412</xdr:colOff>
+      <xdr:row>214</xdr:row>
+      <xdr:rowOff>29882</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>19424</xdr:colOff>
+      <xdr:row>236</xdr:row>
+      <xdr:rowOff>181279</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="56" name="グループ化 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19B995B6-98C7-D063-B413-24DED5FC145C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="488577" y="49909506"/>
+          <a:ext cx="10718800" cy="5279208"/>
+          <a:chOff x="494852" y="48950282"/>
+          <a:chExt cx="10863132" cy="5180597"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="9" name="グループ化 8">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2B1C954-3CDE-0111-D292-86D05AFAB106}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="494852" y="48950282"/>
+            <a:ext cx="10863132" cy="5180597"/>
+            <a:chOff x="477371" y="48706741"/>
+            <a:chExt cx="10804712" cy="5180598"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="2" name="図 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6628907-6B5B-FD07-FEC7-57805877FF59}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="477371" y="48706741"/>
+              <a:ext cx="10804712" cy="5180598"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
               <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3" name="正方形/長方形 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30A5B41C-2C27-49CB-AA8A-912A8FE740E3}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1801532" y="49961801"/>
+              <a:ext cx="2532156" cy="198717"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4" name="吹き出し: 四角形 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3F86FF4-84B0-412F-BF48-1FE088B6FEE6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="878727" y="52565485"/>
+              <a:ext cx="2170580" cy="666190"/>
+            </a:xfrm>
+            <a:prstGeom prst="wedgeRectCallout">
+              <a:avLst>
+                <a:gd name="adj1" fmla="val -8906"/>
+                <a:gd name="adj2" fmla="val 81250"/>
+              </a:avLst>
+            </a:prstGeom>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent2"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent2"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1000">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>common_codes</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>シート側でも処理結果は成功となっています。</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="5" name="正方形/長方形 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E287D2A6-70F9-F934-BD63-AAF340A68FB0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1361515" y="53443094"/>
+              <a:ext cx="1827306" cy="258484"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="55" name="図 54">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3FCA9AA-E5D8-4BB4-90DB-4BE553DAF554}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="6332220" y="50055780"/>
+            <a:ext cx="2171700" cy="167640"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -4559,12 +4951,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{758C1087-7522-4DC4-A1A0-48CB557D7600}">
   <dimension ref="A2:B619"/>
-  <sheetFormatPr defaultColWidth="3.08203125" defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="3.09765625" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="16384" width="3.08203125" style="1"/>
+    <col min="1" max="16384" width="3.09765625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -4572,34 +4964,34 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B3" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B5" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B6" s="2"/>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B35" s="2"/>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B41" s="2"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B42" s="2"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
         <v>0</v>
       </c>
@@ -4607,36 +4999,36 @@
         <v>54</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B44" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B45" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B46" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B47" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="64" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B64" s="2"/>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B66" s="5"/>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B67" s="5"/>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A78" s="1" t="s">
         <v>0</v>
       </c>
@@ -4644,40 +5036,40 @@
         <v>59</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B79" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B80" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B81" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B82" s="2"/>
     </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B92" s="2"/>
     </row>
-    <row r="95" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B95" s="2"/>
     </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B97" s="6"/>
     </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B106" s="2"/>
     </row>
-    <row r="110" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B110" s="2"/>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A120" s="1" t="s">
         <v>0</v>
       </c>
@@ -4685,34 +5077,34 @@
         <v>62</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B121" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B122" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B123" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B125" s="2"/>
     </row>
-    <row r="129" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B129" s="2"/>
     </row>
-    <row r="131" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B131" s="7"/>
     </row>
-    <row r="139" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B139" s="2"/>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A151" s="1" t="s">
         <v>0</v>
       </c>
@@ -4720,44 +5112,44 @@
         <v>66</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B152" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B153" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B154" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B155" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B156" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="161" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B161" s="2"/>
     </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="163" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B163" s="4"/>
     </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="165" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B165" s="2"/>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B180" s="2"/>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A181" s="1" t="s">
         <v>0</v>
       </c>
@@ -4765,38 +5157,38 @@
         <v>72</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B182" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B183" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B184" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B185" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B186" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="193" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B193" s="2"/>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B209" s="2"/>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A210" s="1" t="s">
         <v>0</v>
       </c>
@@ -4804,37 +5196,37 @@
         <v>99</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B211" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="212" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B212" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="213" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B213" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="215" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B215" s="2"/>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="216" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B216" s="2"/>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="217" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B217" s="2"/>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="218" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B218" s="2"/>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="219" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B219" s="2"/>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="240" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A240" s="1" t="s">
         <v>0</v>
       </c>
@@ -4842,62 +5234,62 @@
         <v>98</v>
       </c>
     </row>
-    <row r="241" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="241" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B241" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="242" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="242" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B242" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="243" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="243" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B243" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="244" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="244" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B244" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="245" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="245" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B245" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="246" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="246" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B246" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="247" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="247" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B247" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="248" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="248" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B248" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="256" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="256" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B256" s="2"/>
     </row>
-    <row r="264" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="264" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B264" s="2"/>
     </row>
-    <row r="272" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="272" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B272" s="2"/>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="285" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B285" s="2"/>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="286" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B286" s="2"/>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="287" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A287" s="1" t="s">
         <v>0</v>
       </c>
@@ -4905,37 +5297,37 @@
         <v>94</v>
       </c>
     </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="288" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B288" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="289" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="289" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B289" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="290" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="290" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B290" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="294" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="294" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B294" s="2"/>
     </row>
-    <row r="298" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="298" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B298" s="2"/>
     </row>
-    <row r="317" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="317" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B317" s="2"/>
     </row>
-    <row r="329" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="329" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B329" s="2"/>
     </row>
-    <row r="332" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="332" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B332" s="2"/>
     </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="339" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A339" s="1" t="s">
         <v>0</v>
       </c>
@@ -4943,30 +5335,30 @@
         <v>95</v>
       </c>
     </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="340" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B340" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="341" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B341" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="342" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B342" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="343" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B343" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="371" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="371" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B371" s="2"/>
     </row>
-    <row r="373" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="373" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A373" s="1" t="s">
         <v>0</v>
       </c>
@@ -4974,58 +5366,58 @@
         <v>96</v>
       </c>
     </row>
-    <row r="374" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="374" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B374" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="375" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="375" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B375" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="376" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="376" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B376" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="377" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="377" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B377" s="2"/>
     </row>
-    <row r="402" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="402" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B402" s="2"/>
     </row>
-    <row r="406" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="406" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B406" s="2"/>
     </row>
-    <row r="411" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="411" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B411" s="2"/>
     </row>
-    <row r="429" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="429" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B429" s="2"/>
     </row>
-    <row r="430" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="430" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B430" s="2"/>
     </row>
-    <row r="456" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="456" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B456" s="2"/>
     </row>
-    <row r="465" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="465" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B465" s="2"/>
     </row>
-    <row r="482" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="482" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B482" s="2"/>
     </row>
-    <row r="515" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="515" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B515" s="2"/>
     </row>
-    <row r="557" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="557" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B557" s="2"/>
     </row>
-    <row r="584" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="584" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B584" s="2"/>
     </row>
-    <row r="619" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="619" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B619" s="2"/>
     </row>
   </sheetData>
@@ -5039,12 +5431,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16622AB1-2853-4282-ACE0-64F3E064F651}">
   <dimension ref="A2:B589"/>
-  <sheetFormatPr defaultColWidth="3.08203125" defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="3.09765625" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="16384" width="3.08203125" style="1"/>
+    <col min="1" max="16384" width="3.09765625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -5052,30 +5444,30 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B31" s="2"/>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
         <v>0</v>
       </c>
@@ -5083,28 +5475,28 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B38" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B39" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B40" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B42" s="2"/>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B47" s="2"/>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A69" s="1" t="s">
         <v>0</v>
       </c>
@@ -5112,28 +5504,28 @@
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B70" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B71" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B72" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B87" s="2"/>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B97" s="2"/>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A100" s="1" t="s">
         <v>0</v>
       </c>
@@ -5141,26 +5533,26 @@
         <v>19</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B101" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B102" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B111" s="2"/>
     </row>
-    <row r="115" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B115" s="2"/>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B130" s="2"/>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A134" s="1" t="s">
         <v>0</v>
       </c>
@@ -5168,20 +5560,20 @@
         <v>17</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B135" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B136" s="7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B144" s="2"/>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A164" s="1" t="s">
         <v>0</v>
       </c>
@@ -5189,23 +5581,23 @@
         <v>18</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B165" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B166" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B168" s="2"/>
     </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="183" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B183" s="2"/>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A194" s="1" t="s">
         <v>0</v>
       </c>
@@ -5213,33 +5605,33 @@
         <v>23</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B195" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B196" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B197" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B198" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="210" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="210" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B210" s="2"/>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="229" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B229" s="2"/>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="237" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A237" s="1" t="s">
         <v>0</v>
       </c>
@@ -5247,26 +5639,26 @@
         <v>26</v>
       </c>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="238" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B238" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="239" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B239" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="245" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="245" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B245" s="2"/>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="258" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B258" s="2"/>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="267" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B267" s="2"/>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="271" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A271" s="1" t="s">
         <v>0</v>
       </c>
@@ -5274,38 +5666,38 @@
         <v>29</v>
       </c>
     </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="272" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B272" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="273" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="273" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B273" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="274" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="274" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B274" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="275" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="275" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B275" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="276" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="276" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B276" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="290" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="290" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B290" s="2"/>
     </row>
-    <row r="302" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="302" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B302" s="2"/>
     </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="305" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A305" s="1" t="s">
         <v>0</v>
       </c>
@@ -5313,31 +5705,31 @@
         <v>34</v>
       </c>
     </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="306" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B306" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="307" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B307" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="308" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B308" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="312" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B312" s="2"/>
     </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="341" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B341" s="2"/>
     </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="344" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B344" s="3"/>
     </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="347" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A347" s="1" t="s">
         <v>0</v>
       </c>
@@ -5345,25 +5737,25 @@
         <v>40</v>
       </c>
     </row>
-    <row r="348" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="348" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B348" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="349" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="349" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B349" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="350" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B350" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="372" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="372" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B372" s="2"/>
     </row>
-    <row r="376" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="376" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A376" s="1" t="s">
         <v>0</v>
       </c>
@@ -5371,54 +5763,54 @@
         <v>44</v>
       </c>
     </row>
-    <row r="377" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="377" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B377" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="378" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="378" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B378" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="379" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="379" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B379" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="380" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="380" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B380" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="381" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="381" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B381" s="2"/>
     </row>
-    <row r="399" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="399" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B399" s="2"/>
     </row>
-    <row r="400" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="400" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B400" s="2"/>
     </row>
-    <row r="426" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="426" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B426" s="2"/>
     </row>
-    <row r="435" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="435" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B435" s="2"/>
     </row>
-    <row r="452" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="452" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B452" s="2"/>
     </row>
-    <row r="485" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="485" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B485" s="2"/>
     </row>
-    <row r="527" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="527" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B527" s="2"/>
     </row>
-    <row r="554" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="554" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B554" s="2"/>
     </row>
-    <row r="589" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="589" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B589" s="2"/>
     </row>
   </sheetData>
